--- a/Web_zhilian/temp/test_20241210.xlsx
+++ b/Web_zhilian/temp/test_20241210.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="38">
   <si>
     <t xml:space="preserve">CREDATE</t>
   </si>
@@ -62,12 +62,36 @@
     <t xml:space="preserve">TOTAL_LINE</t>
   </si>
   <si>
+    <t xml:space="preserve">2024/8/7 17:30:44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">康泽药业连锁有限公司</t>
+  </si>
+  <si>
+    <t xml:space="preserve">瑞舒伐他汀钙胶囊</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鲁南贝特制药有限公司</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5mg*14片</t>
+  </si>
+  <si>
+    <t xml:space="preserve">盒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48221201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0001/1/1 0:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11/30 0:00:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">2024/11/30 11:57:55</t>
   </si>
   <si>
-    <t xml:space="preserve">康泽药业连锁有限公司</t>
-  </si>
-  <si>
     <t xml:space="preserve">小儿消积止咳口服液</t>
   </si>
   <si>
@@ -77,13 +101,7 @@
     <t xml:space="preserve">10ml*10袋</t>
   </si>
   <si>
-    <t xml:space="preserve">盒</t>
-  </si>
-  <si>
     <t xml:space="preserve">B68241501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0001/1/1 0:00:00</t>
   </si>
   <si>
     <t xml:space="preserve">2026/8/31 0:00:00</t>
@@ -152,13 +170,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.900000000000002" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.05" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -225,7 +244,7 @@
         <v>17</v>
       </c>
       <c r="E2" s="0">
-        <v>9803</v>
+        <v>5329</v>
       </c>
       <c r="F2" s="0" t="s">
         <v>18</v>
@@ -250,18 +269,18 @@
         <v>24</v>
       </c>
       <c r="N2" s="0">
-        <v>500</v>
+        <v>87</v>
       </c>
       <c r="O2" s="0">
-        <v>33.85</v>
+        <v>27.04</v>
       </c>
       <c r="P2" s="0">
-        <v>16925</v>
+        <v>2352.48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B3" s="0">
         <v>0</v>
@@ -276,40 +295,40 @@
         <v>9803</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H3" s="0"/>
       <c r="I3" s="0" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J3" s="0" t="s">
         <v>21</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L3" s="0" t="s">
         <v>23</v>
       </c>
       <c r="M3" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="N3" s="0">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="O3" s="0">
         <v>33.85</v>
       </c>
       <c r="P3" s="0">
-        <v>10155</v>
+        <v>16925</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4" s="0">
         <v>0</v>
@@ -324,40 +343,40 @@
         <v>9803</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H4" s="0"/>
       <c r="I4" s="0" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J4" s="0" t="s">
         <v>21</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L4" s="0" t="s">
         <v>23</v>
       </c>
       <c r="M4" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N4" s="0">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="O4" s="0">
-        <v>48.84</v>
+        <v>33.85</v>
       </c>
       <c r="P4" s="0">
-        <v>29304</v>
+        <v>10155</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B5" s="0">
         <v>0</v>
@@ -372,34 +391,82 @@
         <v>9803</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H5" s="0"/>
       <c r="I5" s="0" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J5" s="0" t="s">
         <v>21</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L5" s="0" t="s">
         <v>23</v>
       </c>
       <c r="M5" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="N5" s="0">
-        <v>840</v>
+        <v>600</v>
       </c>
       <c r="O5" s="0">
         <v>48.84</v>
       </c>
       <c r="P5" s="0">
+        <v>29304</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="0">
+        <v>0</v>
+      </c>
+      <c r="C6" s="0">
+        <v>4278</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="0">
+        <v>9803</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="0"/>
+      <c r="I6" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="N6" s="0">
+        <v>840</v>
+      </c>
+      <c r="O6" s="0">
+        <v>48.84</v>
+      </c>
+      <c r="P6" s="0">
         <v>41025.6</v>
       </c>
     </row>
